--- a/academias/Física - Estadisticos 20211.xlsx
+++ b/academias/Física - Estadisticos 20211.xlsx
@@ -1133,22 +1133,25 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I8">
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1552,19 +1555,19 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H8">
-        <v>26.32</v>
+        <v>21.05</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>

--- a/academias/Física - Estadisticos 20211.xlsx
+++ b/academias/Física - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,6 +100,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -152,8 +156,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -454,42 +460,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -512,19 +521,19 @@
       <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>14.29</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -547,19 +556,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>69.23</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>30.77</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>6.2</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>3.85</v>
       </c>
     </row>
@@ -582,19 +591,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="1">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>8</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -617,19 +626,19 @@
       <c r="F5">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>62.5</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>37.5</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.9</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>12.5</v>
       </c>
     </row>
@@ -652,19 +661,19 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>94.12</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>5.88</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -687,19 +696,19 @@
       <c r="F7">
         <v>9</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>75</v>
       </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
-      <c r="I7">
+      <c r="H7" s="1">
+        <v>25</v>
+      </c>
+      <c r="I7" s="2">
         <v>7.2</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>8.33</v>
       </c>
     </row>
@@ -722,19 +731,19 @@
       <c r="F8">
         <v>10</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>73.68000000000001</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>26.32</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -757,19 +766,19 @@
       <c r="F9">
         <v>15</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>34.78</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>65.22</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.2</v>
       </c>
       <c r="J9">
         <v>7</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>30.43</v>
       </c>
     </row>
@@ -792,19 +801,19 @@
       <c r="F10">
         <v>16</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>48.39</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>51.61</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>6.2</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>3.23</v>
       </c>
     </row>
@@ -827,19 +836,19 @@
       <c r="F11">
         <v>22</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>42.11</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>57.89</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7</v>
       </c>
       <c r="J11">
         <v>16</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>42.11</v>
       </c>
     </row>
@@ -862,19 +871,19 @@
       <c r="F12">
         <v>20</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>39.39</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>60.61</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.4</v>
       </c>
       <c r="J12">
         <v>13</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>39.39</v>
       </c>
     </row>
@@ -888,42 +897,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -946,16 +958,16 @@
       <c r="F2">
         <v>35</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
         <v>100</v>
       </c>
       <c r="J2">
         <v>35</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>100</v>
       </c>
     </row>
@@ -978,16 +990,16 @@
       <c r="F3">
         <v>26</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
         <v>100</v>
       </c>
       <c r="J3">
         <v>26</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1010,16 +1022,16 @@
       <c r="F4">
         <v>23</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
         <v>100</v>
       </c>
       <c r="J4">
         <v>23</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1042,16 +1054,16 @@
       <c r="F5">
         <v>32</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>100</v>
       </c>
       <c r="J5">
         <v>32</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1074,16 +1086,16 @@
       <c r="F6">
         <v>34</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>100</v>
       </c>
       <c r="J6">
         <v>34</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1106,16 +1118,16 @@
       <c r="F7">
         <v>36</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>100</v>
       </c>
       <c r="J7">
         <v>36</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1138,19 +1150,19 @@
       <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>78.95</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>21.05</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1173,16 +1185,16 @@
       <c r="F9">
         <v>23</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>100</v>
       </c>
       <c r="J9">
         <v>23</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1205,16 +1217,16 @@
       <c r="F10">
         <v>31</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>100</v>
       </c>
       <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1237,16 +1249,16 @@
       <c r="F11">
         <v>38</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>100</v>
       </c>
       <c r="J11">
         <v>38</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1269,16 +1281,16 @@
       <c r="F12">
         <v>33</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>100</v>
       </c>
       <c r="J12">
         <v>33</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1292,42 +1304,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1350,19 +1365,19 @@
       <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>14.29</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1385,19 +1400,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>69.23</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>30.77</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>6.2</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>3.85</v>
       </c>
     </row>
@@ -1420,19 +1435,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="1">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>8</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1455,19 +1470,19 @@
       <c r="F5">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>62.5</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>37.5</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.9</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>12.5</v>
       </c>
     </row>
@@ -1490,19 +1505,19 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>94.12</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>5.88</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1525,19 +1540,19 @@
       <c r="F7">
         <v>9</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>75</v>
       </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
-      <c r="I7">
+      <c r="H7" s="1">
+        <v>25</v>
+      </c>
+      <c r="I7" s="2">
         <v>7.2</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>8.33</v>
       </c>
     </row>
@@ -1560,19 +1575,19 @@
       <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>78.95</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>21.05</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1595,19 +1610,19 @@
       <c r="F9">
         <v>15</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>34.78</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>65.22</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.2</v>
       </c>
       <c r="J9">
         <v>7</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>30.43</v>
       </c>
     </row>
@@ -1630,19 +1645,19 @@
       <c r="F10">
         <v>16</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>48.39</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>51.61</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>6.2</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>3.23</v>
       </c>
     </row>
@@ -1665,19 +1680,19 @@
       <c r="F11">
         <v>22</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>42.11</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>57.89</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7</v>
       </c>
       <c r="J11">
         <v>16</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>42.11</v>
       </c>
     </row>
@@ -1700,19 +1715,19 @@
       <c r="F12">
         <v>20</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>39.39</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>60.61</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.4</v>
       </c>
       <c r="J12">
         <v>13</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>39.39</v>
       </c>
     </row>

--- a/academias/Física - Estadisticos 20211.xlsx
+++ b/academias/Física - Estadisticos 20211.xlsx
@@ -101,7 +101,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Física - Estadisticos 20211.xlsx
+++ b/academias/Física - Estadisticos 20211.xlsx
@@ -773,13 +773,13 @@
         <v>65.22</v>
       </c>
       <c r="I9" s="2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -811,10 +811,10 @@
         <v>6.2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -843,13 +843,13 @@
         <v>57.89</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J11">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -878,13 +878,13 @@
         <v>60.61</v>
       </c>
       <c r="I12" s="2">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1180,22 +1180,25 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>30.43</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>69.56999999999999</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5.3</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1212,22 +1215,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>38.71</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>61.29</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.1</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1244,22 +1250,25 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>31.58</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>68.42</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5.8</v>
       </c>
       <c r="J11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1276,22 +1285,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>21.21</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5.2</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1605,25 +1617,25 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>34.78</v>
+        <v>30.43</v>
       </c>
       <c r="H9" s="1">
-        <v>65.22</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="I9" s="2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1640,25 +1652,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>48.39</v>
+        <v>38.71</v>
       </c>
       <c r="H10" s="1">
-        <v>51.61</v>
+        <v>61.29</v>
       </c>
       <c r="I10" s="2">
         <v>6.2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1675,25 +1687,25 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1">
-        <v>42.11</v>
+        <v>31.58</v>
       </c>
       <c r="H11" s="1">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1710,25 +1722,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1">
-        <v>39.39</v>
+        <v>21.21</v>
       </c>
       <c r="H12" s="1">
-        <v>60.61</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20211.xlsx
+++ b/academias/Física - Estadisticos 20211.xlsx
@@ -566,10 +566,10 @@
         <v>6.2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -633,13 +633,13 @@
         <v>37.5</v>
       </c>
       <c r="I5" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -703,13 +703,13 @@
         <v>25</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -953,22 +953,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -985,22 +988,25 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>53.85</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>46.15</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1017,22 +1023,25 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>82.61</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>17.39</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1049,22 +1058,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>46.88</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1081,22 +1093,25 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1113,22 +1128,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>36.11</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1407,25 +1425,25 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>69.23</v>
+        <v>53.85</v>
       </c>
       <c r="H3" s="1">
-        <v>30.77</v>
+        <v>46.15</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1442,19 +1460,19 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>82.61</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>17.39</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1477,25 +1495,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>62.5</v>
+        <v>56.25</v>
       </c>
       <c r="H5" s="1">
-        <v>37.5</v>
+        <v>43.75</v>
       </c>
       <c r="I5" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1512,16 +1530,16 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>5.88</v>
+        <v>11.76</v>
       </c>
       <c r="I6" s="2">
         <v>7.6</v>
@@ -1547,25 +1565,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="H7" s="1">
-        <v>25</v>
+        <v>30.56</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">

--- a/academias/Física - Estadisticos 20211.xlsx
+++ b/academias/Física - Estadisticos 20211.xlsx
@@ -965,13 +965,13 @@
         <v>14.29</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1058,25 +1058,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>53.13</v>
+        <v>56.25</v>
       </c>
       <c r="H5" s="1">
-        <v>46.88</v>
+        <v>43.75</v>
       </c>
       <c r="I5" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1402,7 +1402,7 @@
         <v>14.29</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1460,16 +1460,16 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>82.61</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>17.39</v>
+        <v>4.35</v>
       </c>
       <c r="I4" s="2">
         <v>7.7</v>
@@ -1495,19 +1495,19 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>56.25</v>
+        <v>84.38</v>
       </c>
       <c r="H5" s="1">
-        <v>43.75</v>
+        <v>15.63</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1600,19 +1600,19 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>78.95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>21.05</v>
+        <v>5.26</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1635,16 +1635,16 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1">
-        <v>30.43</v>
+        <v>47.83</v>
       </c>
       <c r="H9" s="1">
-        <v>69.56999999999999</v>
+        <v>52.17</v>
       </c>
       <c r="I9" s="2">
         <v>5.6</v>
@@ -1670,19 +1670,19 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1">
-        <v>38.71</v>
+        <v>54.84</v>
       </c>
       <c r="H10" s="1">
-        <v>61.29</v>
+        <v>45.16</v>
       </c>
       <c r="I10" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1705,19 +1705,19 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G11" s="1">
-        <v>31.58</v>
+        <v>44.74</v>
       </c>
       <c r="H11" s="1">
-        <v>68.42</v>
+        <v>55.26</v>
       </c>
       <c r="I11" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1">
-        <v>21.21</v>
+        <v>24.24</v>
       </c>
       <c r="H12" s="1">
-        <v>78.79000000000001</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="I12" s="2">
         <v>5.5</v>

--- a/academias/Física - Estadisticos 20211.xlsx
+++ b/academias/Física - Estadisticos 20211.xlsx
@@ -1000,13 +1000,13 @@
         <v>46.15</v>
       </c>
       <c r="I3" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1105,13 +1105,13 @@
         <v>11.76</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1128,25 +1128,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>63.89</v>
+        <v>72.22</v>
       </c>
       <c r="H7" s="1">
-        <v>36.11</v>
+        <v>27.78</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1425,19 +1425,19 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>53.85</v>
+        <v>76.92</v>
       </c>
       <c r="H3" s="1">
-        <v>46.15</v>
+        <v>23.08</v>
       </c>
       <c r="I3" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1530,19 +1530,19 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>11.76</v>
+        <v>8.82</v>
       </c>
       <c r="I6" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1565,16 +1565,16 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>69.44</v>
+        <v>86.11</v>
       </c>
       <c r="H7" s="1">
-        <v>30.56</v>
+        <v>13.89</v>
       </c>
       <c r="I7" s="2">
         <v>6.9</v>
